--- a/xls/square_20_tri3_18.xlsx
+++ b/xls/square_20_tri3_18.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16">
+        <v>361</v>
+      </c>
+      <c r="C16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16">
+        <v>441</v>
+      </c>
+      <c r="E16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16">
+        <v>289</v>
+      </c>
+      <c r="G16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16">
+        <v>1536</v>
+      </c>
+      <c r="I16">
+        <v>2.8658487328695177</v>
+      </c>
+      <c r="J16">
+        <v>-0.4638806198350695</v>
+      </c>
+      <c r="K16">
+        <v>0.7714217693011007</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17">
+        <v>361</v>
+      </c>
+      <c r="C17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17">
+        <v>441</v>
+      </c>
+      <c r="E17" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17">
+        <v>324</v>
+      </c>
+      <c r="G17" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17">
+        <v>1734</v>
+      </c>
+      <c r="I17">
+        <v>1.7160680146781484</v>
+      </c>
+      <c r="J17">
+        <v>-1.2226336287385835</v>
+      </c>
+      <c r="K17">
+        <v>0.16450043259925246</v>
+      </c>
+    </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
         <v>11</v>
